--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaggarwal/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/IL/trans/SoCDTtiNTY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEF7BEF7-F9D0-4B41-9B67-9FA0E1343C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE1583E-2085-4BE7-B456-43253B7BD58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>SoCDTtiNTY Share of Cargo Dist Transported that is New This Year</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>hydrogen vehicle</t>
-  </si>
-  <si>
-    <t>Illinois</t>
   </si>
 </sst>
 </file>
@@ -157,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -169,7 +166,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -188,7 +184,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -508,21 +504,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="5">
-        <v>44907</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -530,47 +520,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -586,13 +576,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" customWidth="1"/>
-    <col min="2" max="8" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -618,7 +608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -644,7 +634,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -670,7 +660,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -696,7 +686,7 @@
         <v>4.1599999999999998E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -722,7 +712,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -748,7 +738,7 @@
         <v>2.9819999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -785,13 +775,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" customWidth="1"/>
-    <col min="2" max="8" width="14.5" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -817,7 +807,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -843,7 +833,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -869,7 +859,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -895,7 +885,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -921,7 +911,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -947,7 +937,7 @@
         <v>3.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>

--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11201"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaggarwal/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/IL/trans/SoCDTtiNTY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE1583E-2085-4BE7-B456-43253B7BD58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEF7BEF7-F9D0-4B41-9B67-9FA0E1343C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
     <t>SoCDTtiNTY Share of Cargo Dist Transported that is New This Year</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>hydrogen vehicle</t>
+  </si>
+  <si>
+    <t>Illinois</t>
   </si>
 </sst>
 </file>
@@ -154,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -166,6 +169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -184,7 +188,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -504,15 +508,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="5">
+        <v>44907</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -520,47 +530,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -576,13 +586,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" customWidth="1"/>
+    <col min="2" max="8" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -608,7 +618,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -634,7 +644,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -660,7 +670,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -686,7 +696,7 @@
         <v>4.1599999999999998E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -712,7 +722,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -738,7 +748,7 @@
         <v>2.9819999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -775,13 +785,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" customWidth="1"/>
+    <col min="2" max="8" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -807,7 +817,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -833,7 +843,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -859,7 +869,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -885,7 +895,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -911,7 +921,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -937,7 +947,7 @@
         <v>3.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>

--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaggarwal/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/IL/trans/SoCDTtiNTY/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/IL/trans/SoCDTtiNTY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEF7BEF7-F9D0-4B41-9B67-9FA0E1343C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA6080A0-ADE2-8E46-BEB9-D17AA255B9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="15980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -188,9 +188,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -228,9 +228,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -263,26 +263,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -315,26 +298,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -519,7 +485,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="5">
-        <v>44907</v>
+        <v>45295</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
